--- a/www/download/IND.surplus_value.empe_ls.r.pc.rpA2.xlsx
+++ b/www/download/IND.surplus_value.empe_ls.r.pc.rpA2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>0.0925722622722338</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>0.0433307526704858</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>8.69</t>
+          <t>0.0869494678223299</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8.06</t>
+          <t>0.0805687443491936</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.0106437113376621</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>0.0342083709092844</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.08</t>
+          <t>0.0507558871809044</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-0.0113678840764578</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-0.07436031397738</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-18.3</t>
+          <t>-0.18300065007942</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-22.2</t>
+          <t>-0.221976815549227</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-21.3</t>
+          <t>-0.213012847767688</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-23.55</t>
+          <t>-0.235523260154675</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-17.6</t>
+          <t>-0.175954380903797</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-15.12</t>
+          <t>-0.151164769112563</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-24.5</t>
+          <t>-0.244981598740527</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-22.58</t>
+          <t>-0.225768365598087</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-0.106380551291873</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-11.46</t>
+          <t>-0.114608035406132</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>-0.127293837698784</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-0.100200999833377</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-11.29</t>
+          <t>-0.112932340133663</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-13.66</t>
+          <t>-0.136567735164549</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-37.86</t>
+          <t>-0.37859745947045</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-0.247115100632712</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-0.247913011651782</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-24.51</t>
+          <t>-0.245050940136959</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-19.63</t>
+          <t>-0.196337802879219</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-12.89</t>
+          <t>-0.128888993700271</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-8.02</t>
+          <t>-0.0802435916283587</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-52.41</t>
+          <t>-0.524067524469179</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-53.77</t>
+          <t>-0.53773020830399</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-51.19</t>
+          <t>-0.511860199456345</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-51.37</t>
+          <t>-0.51368681335357</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-55.93</t>
+          <t>-0.559284464426745</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-56.82</t>
+          <t>-0.568150574584892</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-59.57</t>
+          <t>-0.595653794457791</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-63.36</t>
+          <t>-0.633641241688837</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-73.62</t>
+          <t>-0.736201363260347</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-71.28</t>
+          <t>-0.712768838930998</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-70.64</t>
+          <t>-0.7064269228059</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-70.09</t>
+          <t>-0.700896679914326</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-67.59</t>
+          <t>-0.675866066641681</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-64.79</t>
+          <t>-0.647930595327888</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-67.1</t>
+          <t>-0.670956422632486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>185.06</t>
+          <t>1.85063997552289</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>206.2</t>
+          <t>2.06197876612501</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>253.39</t>
+          <t>2.5338934414544</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>189.78</t>
+          <t>1.89783353733043</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>208.75</t>
+          <t>2.08752794272349</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>244.99</t>
+          <t>2.44986340350926</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>242.14</t>
+          <t>2.42144134159386</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>248.51</t>
+          <t>2.48507719066002</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>194.68</t>
+          <t>1.94677423227647</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>251.47</t>
+          <t>2.51474165674571</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>267.31</t>
+          <t>2.67307768820692</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>268.74</t>
+          <t>2.6873945234519</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>231.63</t>
+          <t>2.31627131286901</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>208.41</t>
+          <t>2.08406836464003</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>170.66</t>
+          <t>1.70655871649667</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>338.42</t>
+          <t>3.38416836967617</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>334.25</t>
+          <t>3.34252491508891</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>351.72</t>
+          <t>3.51718590231625</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>347.13</t>
+          <t>3.47127473779454</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>393.87</t>
+          <t>3.93874183013134</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>372.21</t>
+          <t>3.72214332976881</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>380.58</t>
+          <t>3.8058343735742</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>401.85</t>
+          <t>4.01851079758935</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>393.75</t>
+          <t>3.93747791758987</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>372.05</t>
+          <t>3.72049422077144</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>345.84</t>
+          <t>3.45844325262886</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>330.02</t>
+          <t>3.30022924360338</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>315.22</t>
+          <t>3.15221634989529</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>289.74</t>
+          <t>2.89739123052213</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>283.91</t>
+          <t>2.83909759117874</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>18.68</t>
+          <t>0.186792799366903</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>23.76</t>
+          <t>0.237566238709078</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>28.08</t>
+          <t>0.280800342046428</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22.69</t>
+          <t>0.22688834024631</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>19.32</t>
+          <t>0.193219149581352</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>0.10970849798421</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4.76</t>
+          <t>0.0476027020162406</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6.9</t>
+          <t>0.0690111495819508</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>0.0228259312858827</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-0.0113456308598275</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-0.070083894350059</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-0.10061059411134</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-0.0705134391697892</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-0.0628510337984414</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>-0.0165780092000315</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-38.43</t>
+          <t>-0.384306923246944</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-36.35</t>
+          <t>-0.363506653548509</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-33.48</t>
+          <t>-0.334755107298236</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-29.48</t>
+          <t>-0.294782781207151</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-23.89</t>
+          <t>-0.23887135562391</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-16.04</t>
+          <t>-0.160413116478701</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-8.16</t>
+          <t>-0.0815558711168477</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.00412654964133541</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>0.0525362991162608</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.056212873317699</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>9.44</t>
+          <t>0.0944284950574645</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>12.18</t>
+          <t>0.12178440287718</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>0.215335783111186</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>0.206511363723921</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>23.09</t>
+          <t>0.230874606623106</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.247943290066273</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>0.237295996558746</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>40.97</t>
+          <t>0.409735063631192</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>0.347955731075399</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>0.249885679041003</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>29.25</t>
+          <t>0.292457174840585</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20.51</t>
+          <t>0.205118465008872</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>15.72</t>
+          <t>0.157231233477593</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-6.33</t>
+          <t>-0.0633178614626748</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>10.37</t>
+          <t>0.103741511329859</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>0.144907679195158</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>17.4</t>
+          <t>0.17402118750768</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>0.285271385196667</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>10.12</t>
+          <t>0.101242700004825</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>31.92</t>
+          <t>0.319193090328329</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>201.4</t>
+          <t>2.01399131881027</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>112.63</t>
+          <t>1.1262704052123</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>127.77</t>
+          <t>1.27765740560371</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>122.4</t>
+          <t>1.22398403565489</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>123.99</t>
+          <t>1.23988546350669</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>126.06</t>
+          <t>1.26058260473491</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>114.64</t>
+          <t>1.1464051298466</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99.38</t>
+          <t>0.993784623320487</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>27.73</t>
+          <t>0.277322244741697</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>73.94</t>
+          <t>0.739400654519669</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>0.676901849440767</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>73.2</t>
+          <t>0.732045318349423</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>61.94</t>
+          <t>0.61940043784221</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>59.5</t>
+          <t>0.595008397485589</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>82.51</t>
+          <t>0.825110302268708</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-29.74</t>
+          <t>-0.297428940424942</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-22.33</t>
+          <t>-0.223287000750746</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-0.11538249871824</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-15.46</t>
+          <t>-0.154618172819389</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-19.18</t>
+          <t>-0.191835834458761</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-21.64</t>
+          <t>-0.216409621752422</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-21.23</t>
+          <t>-0.212332657461404</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-22.99</t>
+          <t>-0.229932477926873</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-33.21</t>
+          <t>-0.332111329530524</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-29.49</t>
+          <t>-0.294863370744315</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-29.37</t>
+          <t>-0.293657003851195</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-28.87</t>
+          <t>-0.288659204134167</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-30.93</t>
+          <t>-0.309326505044399</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-25.82</t>
+          <t>-0.258226054796062</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-21.46</t>
+          <t>-0.214605278910174</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-44.01</t>
+          <t>-0.440128440267252</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-43.52</t>
+          <t>-0.435180917662957</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-31.03</t>
+          <t>-0.310342320571833</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-34.5</t>
+          <t>-0.344952562841864</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-34.52</t>
+          <t>-0.345165130944585</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-31.07</t>
+          <t>-0.310665521875992</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-33.8</t>
+          <t>-0.338037678881268</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-37.45</t>
+          <t>-0.374507510388696</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-43.46</t>
+          <t>-0.434570017938373</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-43.47</t>
+          <t>-0.434693538284225</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-44.48</t>
+          <t>-0.44483500140711</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-42.99</t>
+          <t>-0.429869059463291</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-47.35</t>
+          <t>-0.473499726821438</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-44.75</t>
+          <t>-0.447456776025768</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-39.99</t>
+          <t>-0.399879659209414</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>0.0304167111822826</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.52</t>
+          <t>0.0552472547995104</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.26</t>
+          <t>0.232579111315149</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>12.98</t>
+          <t>0.129817558413766</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>0.0663820478389843</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>0.0416017891289677</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.00650997989762192</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-5.63</t>
+          <t>-0.0562812180569727</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-23.61</t>
+          <t>-0.236083094850537</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-18.01</t>
+          <t>-0.180119263199244</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-19.04</t>
+          <t>-0.190374465375193</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-21.58</t>
+          <t>-0.215814893003516</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-22.36</t>
+          <t>-0.223571192406516</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-21.46</t>
+          <t>-0.214649702990198</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-13.74</t>
+          <t>-0.137419984499476</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>136.73</t>
+          <t>1.36727371179632</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>125.87</t>
+          <t>1.25869783816357</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>123.67</t>
+          <t>1.23672862766522</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>114.18</t>
+          <t>1.14184148481501</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>125.76</t>
+          <t>1.25755215270918</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>101.48</t>
+          <t>1.01483575962041</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>97.74</t>
+          <t>0.977424941893514</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>56.62</t>
+          <t>0.566247013575205</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.00969882472080674</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>28.05</t>
+          <t>0.280482723070103</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>35.06</t>
+          <t>0.350575002981816</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>32.28</t>
+          <t>0.322765102242649</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>12.25</t>
+          <t>0.122483216887778</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-5.29</t>
+          <t>-0.0528576788120653</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-0.0444291238288157</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-34.67</t>
+          <t>-0.346694554115174</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-35.48</t>
+          <t>-0.354808246635265</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-24.17</t>
+          <t>-0.241735642492927</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-26.31</t>
+          <t>-0.263109170196923</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-26.21</t>
+          <t>-0.262113838952609</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-18.99</t>
+          <t>-0.189863031103566</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-22.17</t>
+          <t>-0.221744771011492</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-22.74</t>
+          <t>-0.227423186180931</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-35.04</t>
+          <t>-0.350367910602156</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-32.53</t>
+          <t>-0.325334571882462</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-33.72</t>
+          <t>-0.337232891019208</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-35.08</t>
+          <t>-0.350803844717659</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-35.76</t>
+          <t>-0.357592255266195</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-36.4</t>
+          <t>-0.363991230636829</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-33.98</t>
+          <t>-0.339764677613522</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-18.26</t>
+          <t>-0.182626243549628</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-0.195739091131712</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-9.65</t>
+          <t>-0.0964931167183911</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-18.44</t>
+          <t>-0.184430183310274</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-24.71</t>
+          <t>-0.247104213303576</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-25.64</t>
+          <t>-0.256374205762722</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-29.79</t>
+          <t>-0.297917282497458</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-34.92</t>
+          <t>-0.349238820519148</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-50.51</t>
+          <t>-0.505096074149974</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-42.72</t>
+          <t>-0.42720649725438</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-43.42</t>
+          <t>-0.434232631288807</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-43.02</t>
+          <t>-0.430239594498608</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-41.16</t>
+          <t>-0.411567572512601</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-40.01</t>
+          <t>-0.400120028457569</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-36.15</t>
+          <t>-0.361472006581148</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.0131375783806513</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-2.6</t>
+          <t>-0.0259810098948873</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.051704477318784</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.0152312290883301</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-7.93</t>
+          <t>-0.0793394659926152</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-0.120221125232555</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-16.83</t>
+          <t>-0.168326650252392</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-21.07</t>
+          <t>-0.210657138620095</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-26.08</t>
+          <t>-0.260824648818568</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-30.06</t>
+          <t>-0.300612622941016</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-30.18</t>
+          <t>-0.30179436317872</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-30.66</t>
+          <t>-0.306579087284476</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-29.94</t>
+          <t>-0.299359668164407</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-22.37</t>
+          <t>-0.223730561348063</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-18</t>
+          <t>-0.179978437909102</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>52.55</t>
+          <t>0.525495032586213</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>48.11</t>
+          <t>0.481141187484175</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>56.93</t>
+          <t>0.569333553400217</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>0.587796628619175</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>54.67</t>
+          <t>0.546741119745241</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>50.65</t>
+          <t>0.506536586710348</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>58.82</t>
+          <t>0.588163571553924</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>37.56</t>
+          <t>0.375644418170865</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>17.49</t>
+          <t>0.174899545075673</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>0.280361171238632</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>0.30296999973017</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>0.231125086736184</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>18.19</t>
+          <t>0.181903903882787</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>13.17</t>
+          <t>0.131689437565958</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>11.71</t>
+          <t>0.117059970605305</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>0.636086360341745</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>73.99</t>
+          <t>0.73985009161269</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>85.87</t>
+          <t>0.8587244861884</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>93.35</t>
+          <t>0.933462634337719</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>94.83</t>
+          <t>0.948278562027212</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>92.95</t>
+          <t>0.929516236457997</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>98.29</t>
+          <t>0.982904634162168</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>84.04</t>
+          <t>0.840371302750009</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>10.05</t>
+          <t>0.100529401047572</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>97.18</t>
+          <t>0.97179554021269</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>99.06</t>
+          <t>0.990586930382389</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>110.67</t>
+          <t>1.10669806254761</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>101.15</t>
+          <t>1.01149427809014</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>127.65</t>
+          <t>1.27649286933355</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>138.46</t>
+          <t>1.38461120832387</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>0.807952889974345</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>73.66</t>
+          <t>0.736619770796908</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>98.04</t>
+          <t>0.980385761960966</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>98.7</t>
+          <t>0.987001298726548</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>95.16</t>
+          <t>0.951557182685824</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>0.917997759711351</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>95.14</t>
+          <t>0.951421032775412</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>98.22</t>
+          <t>0.982243960483641</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>81.62</t>
+          <t>0.816185559103023</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>0.896580380258859</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>83.68</t>
+          <t>0.836777318165856</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>69.76</t>
+          <t>0.697646885275631</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>60.83</t>
+          <t>0.608277048779578</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>63.66</t>
+          <t>0.636632631756052</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>58.9</t>
+          <t>0.588989517286584</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>64.57</t>
+          <t>0.645659855449866</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>79.92</t>
+          <t>0.799224173344962</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>72.09</t>
+          <t>0.720907572132373</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>80.42</t>
+          <t>0.804231461681459</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>85.94</t>
+          <t>0.859354973464257</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>92.22</t>
+          <t>0.922172224810011</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>87.49</t>
+          <t>0.874908394812161</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>87.04</t>
+          <t>0.87036459835222</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>77.14</t>
+          <t>0.771402731787321</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>66.64</t>
+          <t>0.666409973726902</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>0.594348807597724</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>55.67</t>
+          <t>0.556746392627966</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>0.548627893640904</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>59.16</t>
+          <t>0.591570367879613</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>52.16</t>
+          <t>0.521571459397243</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-10.64</t>
+          <t>-0.106440970590365</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>-0.104352912683498</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>0.0394749718063809</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>0.1084138630992</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>12.27</t>
+          <t>0.122701522911573</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>12.93</t>
+          <t>0.129339965165495</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.0389463090290227</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-1.42</t>
+          <t>-0.0141522167536656</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>5.28</t>
+          <t>0.05283011287775</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>10.15</t>
+          <t>0.10146165447261</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>-0.0217362508136407</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9.14</t>
+          <t>0.0913769577359573</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-0.111432526446196</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-16.8</t>
+          <t>-0.168014693544288</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-26.45</t>
+          <t>-0.264516850859234</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-4.35</t>
+          <t>-0.0435366481549273</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-1.51</t>
+          <t>-0.0150760898400104</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9.05</t>
+          <t>0.0905158791677094</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9.93</t>
+          <t>0.0993363753693495</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.22</t>
+          <t>0.0721890970245251</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>0.0745381677960879</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>0.0300504797225987</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.0115343962051527</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-21.79</t>
+          <t>-0.217903311490246</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-16.49</t>
+          <t>-0.16491086489782</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-16.94</t>
+          <t>-0.169399933519943</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-18.25</t>
+          <t>-0.182463315312327</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-16.33</t>
+          <t>-0.163348855487318</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-16.19</t>
+          <t>-0.161876742534886</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-9.42</t>
+          <t>-0.094241505862075</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-19.93</t>
+          <t>-0.199296490936569</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-0.107813197266307</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-3.58</t>
+          <t>-0.0357708956363005</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.65</t>
+          <t>-0.0265261359209589</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-10.1</t>
+          <t>-0.101044236692951</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>-0.154670651824948</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-0.143072783857889</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-10.02</t>
+          <t>-0.100225705312589</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-13.19</t>
+          <t>-0.131873694719184</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-16.08</t>
+          <t>-0.160763317780841</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-15.54</t>
+          <t>-0.155368280676693</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-11.6</t>
+          <t>-0.115952302898118</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>-0.048428693044882</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-0.0520169310743733</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-9.93</t>
+          <t>-0.0992608012756044</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-0.0997060873841957</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-6.72</t>
+          <t>-0.0672078439083309</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>0.0114015656122344</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>0.0336319036402293</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5.34</t>
+          <t>0.0534133479579497</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.0232254316434712</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>9.4</t>
+          <t>0.0939981327300656</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>9.63</t>
+          <t>0.0962922645534805</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>0.0378253598607463</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>0.0375775281506385</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.0128753464119353</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-1.29</t>
+          <t>-0.0129243350955716</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.00981896665349535</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.0680269401172902</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>0.0852756436552666</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>99.67</t>
+          <t>0.996673350925474</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>85.76</t>
+          <t>0.857597995012979</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>81.87</t>
+          <t>0.818663895479369</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>65.51</t>
+          <t>0.655060548149483</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>60.61</t>
+          <t>0.606060172965545</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>64.36</t>
+          <t>0.643581699420447</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>0.614500197392354</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>56.81</t>
+          <t>0.568121322804065</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16.9</t>
+          <t>0.169011695739464</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>58.77</t>
+          <t>0.587678373287051</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>0.541016893949665</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>48.52</t>
+          <t>0.485239131168475</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>0.249112249961824</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>10.99</t>
+          <t>0.109858398977363</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>0.100148845567563</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-34.44</t>
+          <t>-0.344372364029601</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-24.79</t>
+          <t>-0.247898809827534</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-10.06</t>
+          <t>-0.100596707704177</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.6</t>
+          <t>-0.0459834399514016</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-3.12</t>
+          <t>-0.0311875527987242</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.00497511000513917</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.32</t>
+          <t>0.0731690188583962</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-1.54</t>
+          <t>-0.0154465800225984</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-29.23</t>
+          <t>-0.292343401716977</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-11.51</t>
+          <t>-0.115082956028902</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-15.07</t>
+          <t>-0.150712268410977</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-13.22</t>
+          <t>-0.132155680736949</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-0.0328360843498745</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-13.81</t>
+          <t>-0.13805637107672</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>0.0354072521357034</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>86.88</t>
+          <t>0.868796003660483</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>0.787993520556019</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>72.77</t>
+          <t>0.727651911284583</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>79.35</t>
+          <t>0.793521412879535</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>84.33</t>
+          <t>0.843327373209844</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>110.84</t>
+          <t>1.10835078585181</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>117.06</t>
+          <t>1.17061353354134</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>126.42</t>
+          <t>1.2642024299191</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>65.85</t>
+          <t>0.658547407668326</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>116.82</t>
+          <t>1.16823073163013</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>89.87</t>
+          <t>0.898677588526929</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>69.93</t>
+          <t>0.699324473595573</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>53.74</t>
+          <t>0.537407732196111</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>35.72</t>
+          <t>0.357232219077596</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>59.1</t>
+          <t>0.591001916727411</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>365.51</t>
+          <t>3.65512658803481</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>404.52</t>
+          <t>4.04518799238326</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>416.99</t>
+          <t>4.16988375460694</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>392.01</t>
+          <t>3.92012788838565</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>370.46</t>
+          <t>3.70459914763541</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>356.37</t>
+          <t>3.56367005567233</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>317.24</t>
+          <t>3.17240846436263</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>322.81</t>
+          <t>3.22811199280807</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>338.9</t>
+          <t>3.38898298101295</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>347.4</t>
+          <t>3.47404053431013</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>328.61</t>
+          <t>3.28610324381912</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>366.07</t>
+          <t>3.66069957445414</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>386.15</t>
+          <t>3.86150334623233</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>420.61</t>
+          <t>4.20608148663244</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>421.7</t>
+          <t>4.21696780486383</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>57.79</t>
+          <t>0.577939169865004</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>0.47766742358755</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>81.56</t>
+          <t>0.815590350271405</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>0.655970492694631</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>0.463424265835948</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>0.378224943319527</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>0.0408040467285971</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>0.141972028987236</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-15.84</t>
+          <t>-0.158355026283344</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>0.287203983534347</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>0.284606196767848</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>0.312784264269679</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>0.245513636979112</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>0.0763804840890974</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>0.230451548757841</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-53.2</t>
+          <t>-0.531972894226582</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-51.13</t>
+          <t>-0.511295820706299</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-29.37</t>
+          <t>-0.293715874778049</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-40.53</t>
+          <t>-0.405345652562892</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-42.82</t>
+          <t>-0.428231779874084</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-40.58</t>
+          <t>-0.405773847612178</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-46.31</t>
+          <t>-0.463118333545722</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-51.19</t>
+          <t>-0.511927539471574</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-59.17</t>
+          <t>-0.591727408776937</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-50.8</t>
+          <t>-0.508019433817759</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-49.2</t>
+          <t>-0.491953812243901</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-0.48859575202529</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-49.84</t>
+          <t>-0.498353646687073</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-52.97</t>
+          <t>-0.529704038970097</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-52.07</t>
+          <t>-0.520662080841931</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>19.73</t>
+          <t>0.19730413652878</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>15.52</t>
+          <t>0.155239799849046</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>14.7</t>
+          <t>0.146954615800317</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>0.109792134504211</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20.16</t>
+          <t>0.201648486288729</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>0.311766135431639</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>0.634733867706555</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>68.97</t>
+          <t>0.689712891540164</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>20.15</t>
+          <t>0.201491695934551</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>87.38</t>
+          <t>0.873805870148205</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>78.17</t>
+          <t>0.781719080124688</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>84.19</t>
+          <t>0.841891097688142</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>0.914162527370593</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>72.61</t>
+          <t>0.72613232866129</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>84.28</t>
+          <t>0.842825977449665</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>51.42</t>
+          <t>0.514226728422222</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>48.06</t>
+          <t>0.480576029241645</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>74.28</t>
+          <t>0.742803189386093</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>53.31</t>
+          <t>0.53309528244364</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.545543259275822</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>48.85</t>
+          <t>0.488471346800518</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.42759168870077</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>44.34</t>
+          <t>0.443356096218897</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>0.193937015817998</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>0.409880025369491</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>0.426268062797796</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>53.21</t>
+          <t>0.532104220913049</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>49.19</t>
+          <t>0.491894471888359</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>41.08</t>
+          <t>0.410760230179289</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>70.07</t>
+          <t>0.700698829427645</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>114.47</t>
+          <t>1.14465401710078</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>118.51</t>
+          <t>1.18510606354117</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>153.91</t>
+          <t>1.53912126836488</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>0.949984061749807</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>118.06</t>
+          <t>1.18059436380255</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>83.1</t>
+          <t>0.830950789300175</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>64.38</t>
+          <t>0.64382455438641</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>104.97</t>
+          <t>1.04974842445707</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>72.89</t>
+          <t>0.728851056146229</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>125.29</t>
+          <t>1.25286490564866</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>92.44</t>
+          <t>0.924438772289211</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>101.98</t>
+          <t>1.01984568372985</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>85.66</t>
+          <t>0.856553006043605</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>0.706667800060457</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>96.44</t>
+          <t>0.964412571460932</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>59.94</t>
+          <t>0.599372214623599</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>0.494205830112361</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>65.71</t>
+          <t>0.657083738327541</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>0.736824869794033</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>76.34</t>
+          <t>0.763422441488445</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>60.46</t>
+          <t>0.604627448703589</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>70.67</t>
+          <t>0.706681972623638</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>60.74</t>
+          <t>0.607392788056355</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>50.98</t>
+          <t>0.509750928612128</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>49.91</t>
+          <t>0.499112779023192</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>44.39</t>
+          <t>0.443914735375481</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>47.8</t>
+          <t>0.478022284356156</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>0.376115342608841</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>0.213050897960399</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>0.220384366839197</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>216.21</t>
+          <t>2.16213130748618</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>200.42</t>
+          <t>2.00423043006803</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>208.91</t>
+          <t>2.08913253825296</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>205.38</t>
+          <t>2.0537694029171</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>224.66</t>
+          <t>2.24658805575329</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>230.08</t>
+          <t>2.30078638477778</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>217.86</t>
+          <t>2.17856171624287</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>216.32</t>
+          <t>2.16321118352325</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>68.08</t>
+          <t>0.680754738168865</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>135.21</t>
+          <t>1.35211790639642</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>143.12</t>
+          <t>1.43117560565327</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>132.51</t>
+          <t>1.32512935289784</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>92.32</t>
+          <t>0.923241157021382</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>62.71</t>
+          <t>0.627141384892507</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>28.78</t>
+          <t>0.287848183547563</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>15.18</t>
+          <t>0.151797902714224</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>17.86</t>
+          <t>0.178593496155029</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>0.334670706671778</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>26.83</t>
+          <t>0.268326645792834</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>30.82</t>
+          <t>0.308161666758874</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>0.279657332388652</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>22.01</t>
+          <t>0.22008848087851</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>0.179758439624519</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>6.8</t>
+          <t>0.068008418982018</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>10.77</t>
+          <t>0.107667941777613</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>14.65</t>
+          <t>0.146475937799328</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>0.141142756846958</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>8.04</t>
+          <t>0.0804114852121212</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-16.96</t>
+          <t>-0.16957071420536</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-0.141562558393333</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-24.49</t>
+          <t>-0.244947778384968</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-26.64</t>
+          <t>-0.266432988057555</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-16.51</t>
+          <t>-0.165105839221833</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-22.34</t>
+          <t>-0.223359089072564</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-22.46</t>
+          <t>-0.224610446179572</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-30.19</t>
+          <t>-0.301912905431624</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-31.32</t>
+          <t>-0.313156576427259</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-34.29</t>
+          <t>-0.342941021076607</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-45</t>
+          <t>-0.449960566827456</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-42.81</t>
+          <t>-0.428110150246393</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-44.65</t>
+          <t>-0.446547455412329</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-44.83</t>
+          <t>-0.448340670437881</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-48.82</t>
+          <t>-0.488182926947546</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-42.94</t>
+          <t>-0.429449665866196</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-35.35</t>
+          <t>-0.353488681075606</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>151.71</t>
+          <t>1.51712469739496</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>128.1</t>
+          <t>1.28096669049658</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>115.85</t>
+          <t>1.15847671431047</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>109.42</t>
+          <t>1.09422830143341</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>114.84</t>
+          <t>1.14840764080338</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>138.53</t>
+          <t>1.38532964519898</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>169.6</t>
+          <t>1.69601698893546</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>195.69</t>
+          <t>1.95690594568802</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>173.43</t>
+          <t>1.73427642775963</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>151.03</t>
+          <t>1.51031522520867</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>158.14</t>
+          <t>1.5813875829616</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>167.05</t>
+          <t>1.67046262604027</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>158.39</t>
+          <t>1.5838654430598</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>41.78</t>
+          <t>0.417769611405615</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>61.34</t>
+          <t>0.613356071168546</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>15.41</t>
+          <t>0.154139690460438</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>6.34</t>
+          <t>0.0633500168997225</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>19.36</t>
+          <t>0.193551195127537</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>21.4</t>
+          <t>0.213995207837431</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20.21</t>
+          <t>0.202088058233965</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>0.144108273746178</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8.27</t>
+          <t>0.0827440699574939</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>9.47</t>
+          <t>0.0946988434776321</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>9.51</t>
+          <t>0.0950651949565775</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>0.105462690781489</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>8.78</t>
+          <t>0.0877558804353364</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>10.58</t>
+          <t>0.105758818857505</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>19.34</t>
+          <t>0.193391036795111</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>19.14</t>
+          <t>0.19143392823571</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>32.91</t>
+          <t>0.329115668475115</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>22.6</t>
+          <t>0.226044041697404</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>24.2</t>
+          <t>0.241952416964189</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>18.82</t>
+          <t>0.188246527454046</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>0.218111589049399</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>21.23</t>
+          <t>0.212325180153003</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11.76</t>
+          <t>0.117623408827814</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7.27</t>
+          <t>0.0726776244118204</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>0.0516913201246401</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>0.0216597755677737</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>0.0267948359760015</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>4.63</t>
+          <t>0.0463330647941878</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6.14</t>
+          <t>0.0614193412145949</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>0.0980623839153414</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>16.81</t>
+          <t>0.168144882423205</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>16.18</t>
+          <t>0.161769814993923</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>0.0342487308495911</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>0.0609949180540144</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>0.053257702155306</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7.43</t>
+          <t>0.0743335660361681</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>7.93</t>
+          <t>0.079329615577751</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>0.0264912773599357</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4.41</t>
+          <t>0.0440622662134944</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0.0700069449478196</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.0244244648935811</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>12.38</t>
+          <t>0.123818488674506</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>0.0954832046374732</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>8.45</t>
+          <t>0.0844936232762754</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>9.74</t>
+          <t>0.0974349053840715</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>4.49</t>
+          <t>0.0449364450116001</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>13.42</t>
+          <t>0.134191463752858</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4.85</t>
+          <t>0.0485012496005905</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.42</t>
+          <t>0.0842186942804708</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>0.108043550192051</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>13.84</t>
+          <t>0.138444981521225</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>17.48</t>
+          <t>0.174847042228764</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>19.39</t>
+          <t>0.193868487009157</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>0.221597392815757</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>25.48</t>
+          <t>0.254811152580188</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>0.19587566198125</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>25.6</t>
+          <t>0.256021129815599</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>24.45</t>
+          <t>0.244521875061225</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>23.86</t>
+          <t>0.238620123526547</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>26.73</t>
+          <t>0.267262511207787</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>24.62</t>
+          <t>0.246173366566948</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>28.93</t>
+          <t>0.289335585757541</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
